--- a/Ritumati_Google_Sheet_Template.xlsx
+++ b/Ritumati_Google_Sheet_Template.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -538,16 +538,6 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>pads_distributed</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>people_helped</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -555,6 +545,7 @@
           <t>Bokaro</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -569,12 +560,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -583,6 +568,7 @@
           <t>Chatra</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -597,12 +583,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -611,6 +591,7 @@
           <t>Deoghar</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -625,12 +606,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -639,6 +614,7 @@
           <t>Dhanbad</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -653,12 +629,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -667,6 +637,7 @@
           <t>Dumka</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -681,12 +652,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -715,12 +680,6 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -728,6 +687,7 @@
           <t>Garhwa</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -742,12 +702,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -756,6 +710,7 @@
           <t>Giridih</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -770,12 +725,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -784,6 +733,7 @@
           <t>Godda</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -798,12 +748,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -812,6 +756,7 @@
           <t>Gumla</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -826,12 +771,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -840,6 +779,7 @@
           <t>Hazaribagh</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -854,12 +794,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -868,6 +802,7 @@
           <t>Jamtara</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -882,12 +817,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -896,6 +825,7 @@
           <t>Khunti</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -910,12 +840,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -924,6 +848,7 @@
           <t>Koderma</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -938,12 +863,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -952,6 +871,7 @@
           <t>Latehar</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -966,12 +886,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -980,6 +894,7 @@
           <t>Lohardaga</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -994,12 +909,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1008,6 +917,7 @@
           <t>Pakur</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1022,12 +932,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1036,6 +940,7 @@
           <t>Palamu</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1050,12 +955,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1064,6 +963,7 @@
           <t>Ramgarh</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1078,12 +978,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1092,6 +986,7 @@
           <t>Ranchi</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -1106,12 +1001,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1120,6 +1009,7 @@
           <t>Sahibganj</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1134,12 +1024,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1148,6 +1032,7 @@
           <t>Seraikela-Kharsawan</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1162,12 +1047,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1176,6 +1055,7 @@
           <t>Simdega</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1190,12 +1070,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1204,6 +1078,7 @@
           <t>West Singhbhum</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1218,12 +1093,6 @@
         <is>
           <t>TRUE</t>
         </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1639,6 +1508,7 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>First Ritumati update</t>
@@ -1649,6 +1519,7 @@
           <t>Add your latest programme or event update here.</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>FALSE</t>

--- a/Ritumati_Google_Sheet_Template.xlsx
+++ b/Ritumati_Google_Sheet_Template.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -538,6 +538,16 @@
           <t>active</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pads_distributed</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>people_helped</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -545,7 +555,6 @@
           <t>Bokaro</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -560,6 +569,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -568,7 +583,6 @@
           <t>Chatra</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -583,6 +597,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -591,7 +611,6 @@
           <t>Deoghar</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -606,6 +625,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -614,7 +639,6 @@
           <t>Dhanbad</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -629,6 +653,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -637,7 +667,6 @@
           <t>Dumka</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -652,6 +681,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -680,6 +715,12 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -687,7 +728,6 @@
           <t>Garhwa</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -702,6 +742,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -710,7 +756,6 @@
           <t>Giridih</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -725,6 +770,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +784,6 @@
           <t>Godda</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -748,6 +798,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -756,7 +812,6 @@
           <t>Gumla</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -771,6 +826,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -779,7 +840,6 @@
           <t>Hazaribagh</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -794,6 +854,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -802,7 +868,6 @@
           <t>Jamtara</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -817,6 +882,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -825,7 +896,6 @@
           <t>Khunti</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -840,6 +910,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -848,7 +924,6 @@
           <t>Koderma</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -863,6 +938,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -871,7 +952,6 @@
           <t>Latehar</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -886,6 +966,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -894,7 +980,6 @@
           <t>Lohardaga</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -909,6 +994,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -917,7 +1008,6 @@
           <t>Pakur</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -932,6 +1022,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -940,7 +1036,6 @@
           <t>Palamu</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -955,6 +1050,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -963,7 +1064,6 @@
           <t>Ramgarh</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -978,6 +1078,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -986,7 +1092,6 @@
           <t>Ranchi</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -1001,6 +1106,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1009,7 +1120,6 @@
           <t>Sahibganj</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1024,6 +1134,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1032,7 +1148,6 @@
           <t>Seraikela-Kharsawan</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1047,6 +1162,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1055,7 +1176,6 @@
           <t>Simdega</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1070,6 +1190,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1078,7 +1204,6 @@
           <t>West Singhbhum</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1093,6 +1218,12 @@
         <is>
           <t>TRUE</t>
         </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +1639,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>First Ritumati update</t>
@@ -1519,7 +1649,6 @@
           <t>Add your latest programme or event update here.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>FALSE</t>
